--- a/ShinyApp/datasets/scinfer_combined_hs.xlsx
+++ b/ShinyApp/datasets/scinfer_combined_hs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="13"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="scinfer_combined_hs" sheetId="1" state="visible" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="929">
   <si>
     <t>celltype</t>
   </si>
@@ -2552,6 +2552,78 @@
   </si>
   <si>
     <t>CALM1</t>
+  </si>
+  <si>
+    <t>Hepatocytes</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>HNF4A</t>
+  </si>
+  <si>
+    <t>CYP3A4</t>
+  </si>
+  <si>
+    <t>CYP2E1</t>
+  </si>
+  <si>
+    <t>ASGR1</t>
+  </si>
+  <si>
+    <t>FAH</t>
+  </si>
+  <si>
+    <t>Cholangiocytes</t>
+  </si>
+  <si>
+    <t>SOX9</t>
+  </si>
+  <si>
+    <t>SLC4A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endothelial cells</t>
+  </si>
+  <si>
+    <t>CLEC4G</t>
+  </si>
+  <si>
+    <t>LYVE1</t>
+  </si>
+  <si>
+    <t>CD34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupffer cells</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hepatic stellate cells</t>
+  </si>
+  <si>
+    <t>LRAT</t>
+  </si>
+  <si>
+    <t>DES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B / Plasma cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dendritic cells</t>
+  </si>
+  <si>
+    <t>CD1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fibroblasts / Mesenchymal</t>
   </si>
   <si>
     <t>Heart</t>
@@ -2750,7 +2822,7 @@
   <fonts count="6">
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -2760,25 +2832,22 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.000000"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9.000000"/>
       <color rgb="FF212529"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11.000000"/>
+      <name val="__Inter_36bd41"/>
+    </font>
+    <font>
+      <sz val="7.500000"/>
       <color indexed="64"/>
-      <name val="__Inter_36bd41"/>
+      <name val="Liberation Sans"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2801,21 +2870,24 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
@@ -12981,6 +13053,9 @@
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="31.8515625"/>
+  </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
@@ -12997,11 +13072,11 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>142</v>
+      <c r="A2" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>843</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -13011,11 +13086,11 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>137</v>
+      <c r="A3" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>844</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -13025,11 +13100,11 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>222</v>
+      <c r="A4" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>845</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -13039,11 +13114,11 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>223</v>
+      <c r="A5" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>846</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -13053,11 +13128,11 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>224</v>
+      <c r="A6" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>847</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -13067,11 +13142,11 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>225</v>
+      <c r="A7" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -13081,11 +13156,11 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>226</v>
+      <c r="A8" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>848</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -13095,11 +13170,11 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>227</v>
+      <c r="A9" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>590</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
@@ -13109,11 +13184,11 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>228</v>
+      <c r="A10" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
@@ -13123,11 +13198,11 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>229</v>
+      <c r="A11" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>850</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -13137,25 +13212,25 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>231</v>
+      <c r="A12" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="C12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>232</v>
+      <c r="A13" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>851</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
@@ -13165,11 +13240,11 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>233</v>
+      <c r="A14" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>853</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
@@ -13179,11 +13254,11 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>234</v>
+      <c r="A15" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>854</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
@@ -13193,25 +13268,25 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>235</v>
+      <c r="A16" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>855</v>
       </c>
       <c r="C16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>236</v>
+      <c r="A17" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
@@ -13221,11 +13296,11 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>102</v>
+      <c r="A18" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
@@ -13235,11 +13310,11 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>237</v>
+      <c r="A19" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
@@ -13249,11 +13324,11 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>238</v>
+      <c r="A20" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>857</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -13263,11 +13338,11 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>100</v>
+      <c r="A21" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
@@ -13277,11 +13352,11 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>240</v>
+      <c r="A22" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -13291,11 +13366,11 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>241</v>
+      <c r="A23" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>263</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
@@ -13305,11 +13380,11 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>33</v>
+      <c r="A24" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>859</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
@@ -13319,11 +13394,11 @@
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>242</v>
+      <c r="A25" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
@@ -13333,11 +13408,11 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>243</v>
+      <c r="A26" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>860</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -13347,11 +13422,11 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>244</v>
+      <c r="A27" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -13361,11 +13436,11 @@
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>245</v>
+      <c r="A28" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
@@ -13375,11 +13450,11 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>246</v>
+      <c r="A29" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -13389,11 +13464,11 @@
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>247</v>
+      <c r="A30" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -13403,11 +13478,11 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>248</v>
+      <c r="A31" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -13417,11 +13492,11 @@
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>250</v>
+      <c r="A32" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
@@ -13431,11 +13506,11 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>224</v>
+      <c r="A33" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="C33" s="1">
         <v>1</v>
@@ -13445,11 +13520,11 @@
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>225</v>
+      <c r="A34" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="C34" s="1">
         <v>1</v>
@@ -13459,11 +13534,11 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>228</v>
+      <c r="A35" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
@@ -13473,11 +13548,11 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>142</v>
+      <c r="A36" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="C36" s="1">
         <v>1</v>
@@ -13487,11 +13562,11 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>223</v>
+      <c r="A37" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>338</v>
       </c>
       <c r="C37" s="1">
         <v>1</v>
@@ -13501,11 +13576,11 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>222</v>
+      <c r="A38" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>539</v>
       </c>
       <c r="C38" s="1">
         <v>1</v>
@@ -13515,11 +13590,11 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>137</v>
+      <c r="A39" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>544</v>
       </c>
       <c r="C39" s="1">
         <v>1</v>
@@ -13529,11 +13604,11 @@
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>251</v>
+      <c r="A40" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>864</v>
       </c>
       <c r="C40" s="1">
         <v>1</v>
@@ -13543,11 +13618,11 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>252</v>
+      <c r="A41" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>466</v>
       </c>
       <c r="C41" s="1">
         <v>1</v>
@@ -13557,11 +13632,11 @@
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>116</v>
+      <c r="A42" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>524</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
@@ -13571,11 +13646,11 @@
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>119</v>
+      <c r="A43" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="C43" s="1">
         <v>1</v>
@@ -13584,1238 +13659,94 @@
         <v>221</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C44" s="1">
-        <v>1</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="46" ht="13">
-      <c r="A46" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="1">
-        <v>1</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="47" ht="13">
-      <c r="A47" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C47" s="1">
-        <v>1</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="48" ht="13">
-      <c r="A48" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C48" s="1">
-        <v>1</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="49" ht="13">
-      <c r="A49" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C49" s="1">
-        <v>1</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="50" ht="13">
-      <c r="A50" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="51" ht="13">
-      <c r="A51" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C51" s="1">
-        <v>1</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="52" ht="13">
-      <c r="A52" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" ht="13">
-      <c r="A53" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" s="1">
-        <v>1</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="54" ht="13">
-      <c r="A54" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C54" s="1">
-        <v>1</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="55" ht="13">
-      <c r="A55" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C55" s="1">
-        <v>1</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="56" ht="13">
-      <c r="A56" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="57" ht="13">
-      <c r="A57" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C57" s="1">
-        <v>1</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" ht="13">
-      <c r="A58" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C58" s="1">
-        <v>1</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="59" ht="13">
-      <c r="A59" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="60" ht="13">
-      <c r="A60" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60" s="1">
-        <v>1</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="61" ht="13">
-      <c r="A61" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C61" s="1">
-        <v>1</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="62" ht="13">
-      <c r="A62" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C62" s="1">
-        <v>1</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="63" ht="13">
-      <c r="A63" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C63" s="1">
-        <v>1</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" ht="13">
-      <c r="A64" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="65" ht="13">
-      <c r="A65" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" ht="13">
-      <c r="A66" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="67" ht="13">
-      <c r="A67" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="68" ht="13">
-      <c r="A68" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C68" s="1">
-        <v>1</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="69" ht="13">
-      <c r="A69" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C69" s="1">
-        <v>1</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="70" ht="13">
-      <c r="A70" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C70" s="1">
-        <v>1</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="71" ht="13">
-      <c r="A71" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="72" ht="13">
-      <c r="A72" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C72" s="1">
-        <v>1</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="73" ht="13">
-      <c r="A73" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C73" s="1">
-        <v>1</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="74" ht="13">
-      <c r="A74" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C74" s="1">
-        <v>1</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="75" ht="13">
-      <c r="A75" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C75" s="1">
-        <v>1</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="76" ht="13">
-      <c r="A76" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C76" s="1">
-        <v>1</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="77" ht="13">
-      <c r="A77" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C77" s="1">
-        <v>1</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="78" ht="13">
-      <c r="A78" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C78" s="1">
-        <v>1</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="79" ht="13">
-      <c r="A79" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C79" s="1">
-        <v>1</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="80" ht="13">
-      <c r="A80" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C80" s="1">
-        <v>1</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="81" ht="13">
-      <c r="A81" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C81" s="1">
-        <v>1</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="82" ht="13">
-      <c r="A82" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C82" s="1">
-        <v>1</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="83" ht="13">
-      <c r="A83" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C83" s="1">
-        <v>1</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="84" ht="13">
-      <c r="A84" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="85" ht="13">
-      <c r="A85" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C85" s="1">
-        <v>1</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="86" ht="13">
-      <c r="A86" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="87" ht="13">
-      <c r="A87" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="88" ht="13">
-      <c r="A88" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="89" ht="13">
-      <c r="A89" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C89" s="1">
-        <v>1</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="90" ht="13">
-      <c r="A90" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="91" ht="13">
-      <c r="A91" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C91" s="1">
-        <v>1</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="92" ht="13">
-      <c r="A92" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="93" ht="13">
-      <c r="A93" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="94" ht="13">
-      <c r="A94" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="95" ht="13">
-      <c r="A95" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C95" s="1">
-        <v>1</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="96" ht="13">
-      <c r="A96" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C96" s="1">
-        <v>1</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="97" ht="13">
-      <c r="A97" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C97" s="1">
-        <v>1</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="98" ht="13">
-      <c r="A98" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="99" ht="13">
-      <c r="A99" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C99" s="1">
-        <v>1</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="100" ht="13">
-      <c r="A100" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C100" s="1">
-        <v>1</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="101" ht="13">
-      <c r="A101" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C101" s="1">
-        <v>1</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="102" ht="13">
-      <c r="A102" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C102" s="1">
-        <v>1</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="103" ht="13">
-      <c r="A103" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C103" s="1">
-        <v>1</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="104" ht="13">
-      <c r="A104" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C104" s="1">
-        <v>1</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="105" ht="13">
-      <c r="A105" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C105" s="1">
-        <v>1</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="106" ht="13">
-      <c r="A106" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C106" s="1">
-        <v>1</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="107" ht="13">
-      <c r="A107" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C107" s="1">
-        <v>1</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="108" ht="13">
-      <c r="A108" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C108" s="1">
-        <v>1</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="109" ht="13">
-      <c r="A109" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C109" s="1">
-        <v>1</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="110" ht="13">
-      <c r="A110" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C110" s="1">
-        <v>1</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="111" ht="13">
-      <c r="A111" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C111" s="1">
-        <v>1</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="112" ht="13">
-      <c r="A112" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C112" s="1">
-        <v>1</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="113" ht="13">
-      <c r="A113" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C113" s="1">
-        <v>1</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="114" ht="13">
-      <c r="A114" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C114" s="1">
-        <v>1</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="115" ht="13">
-      <c r="A115" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C115" s="1">
-        <v>1</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="116" ht="13">
-      <c r="A116" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C116" s="1">
-        <v>1</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="117" ht="13">
-      <c r="A117" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C117" s="1">
-        <v>1</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="118" ht="13">
-      <c r="A118" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C118" s="1">
-        <v>1</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="119" ht="13">
-      <c r="A119" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C119" s="1">
-        <v>1</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="120" ht="13">
-      <c r="A120" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C120" s="1">
-        <v>1</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="121" ht="13">
-      <c r="A121" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C121" s="1">
-        <v>1</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="122" ht="13">
-      <c r="A122" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C122" s="1">
-        <v>1</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="123" ht="13">
-      <c r="A123" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C123" s="1">
-        <v>1</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="124" ht="13">
-      <c r="A124" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C124" s="1">
-        <v>1</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="125" ht="13">
-      <c r="A125" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C125" s="1">
-        <v>1</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="126" ht="13">
-      <c r="A126" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C126" s="1">
-        <v>1</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="127" ht="13">
-      <c r="A127" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C127" s="1">
-        <v>1</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="128" ht="13">
-      <c r="A128" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C128" s="1">
-        <v>1</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="129" ht="13">
-      <c r="A129" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C129" s="1">
-        <v>1</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="130" ht="13">
-      <c r="A130" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C130" s="1">
-        <v>1</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="131" ht="13">
-      <c r="A131" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C131" s="1">
-        <v>1</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
+    <row r="44" ht="15" customHeight="1"/>
+    <row r="45" ht="15" customHeight="1"/>
+    <row r="46" ht="13"/>
+    <row r="47" ht="13"/>
+    <row r="48" ht="13"/>
+    <row r="49" ht="13"/>
+    <row r="50" ht="13"/>
+    <row r="51" ht="13"/>
+    <row r="52" ht="13"/>
+    <row r="53" ht="13"/>
+    <row r="54" ht="13"/>
+    <row r="55" ht="13"/>
+    <row r="56" ht="13"/>
+    <row r="57" ht="13"/>
+    <row r="58" ht="13"/>
+    <row r="59" ht="13"/>
+    <row r="60" ht="13"/>
+    <row r="61" ht="13"/>
+    <row r="62" ht="13"/>
+    <row r="63" ht="13"/>
+    <row r="64" ht="13"/>
+    <row r="65" ht="13"/>
+    <row r="66" ht="13"/>
+    <row r="67" ht="13"/>
+    <row r="68" ht="13"/>
+    <row r="69" ht="13"/>
+    <row r="70" ht="13"/>
+    <row r="71" ht="13"/>
+    <row r="72" ht="13"/>
+    <row r="73" ht="13"/>
+    <row r="74" ht="13"/>
+    <row r="75" ht="13"/>
+    <row r="76" ht="13"/>
+    <row r="77" ht="13"/>
+    <row r="78" ht="13"/>
+    <row r="79" ht="13"/>
+    <row r="80" ht="13"/>
+    <row r="81" ht="13"/>
+    <row r="82" ht="13"/>
+    <row r="83" ht="13"/>
+    <row r="84" ht="13"/>
+    <row r="85" ht="13"/>
+    <row r="86" ht="13"/>
+    <row r="87" ht="13"/>
+    <row r="88" ht="13"/>
+    <row r="89" ht="13"/>
+    <row r="90" ht="13"/>
+    <row r="91" ht="13"/>
+    <row r="92" ht="13"/>
+    <row r="93" ht="13"/>
+    <row r="94" ht="13"/>
+    <row r="95" ht="13"/>
+    <row r="96" ht="13"/>
+    <row r="97" ht="13"/>
+    <row r="98" ht="13"/>
+    <row r="99" ht="13"/>
+    <row r="100" ht="13"/>
+    <row r="101" ht="13"/>
+    <row r="102" ht="13"/>
+    <row r="103" ht="13"/>
+    <row r="104" ht="13"/>
+    <row r="105" ht="13"/>
+    <row r="106" ht="13"/>
+    <row r="107" ht="13"/>
+    <row r="108" ht="13"/>
+    <row r="109" ht="13"/>
+    <row r="110" ht="13"/>
+    <row r="111" ht="13"/>
+    <row r="112" ht="13"/>
+    <row r="113" ht="13"/>
+    <row r="114" ht="13"/>
+    <row r="115" ht="13"/>
+    <row r="116" ht="13"/>
+    <row r="117" ht="13"/>
+    <row r="118" ht="13"/>
+    <row r="119" ht="13"/>
+    <row r="120" ht="13"/>
+    <row r="121" ht="13"/>
+    <row r="122" ht="13"/>
+    <row r="123" ht="13"/>
+    <row r="124" ht="13"/>
+    <row r="125" ht="13"/>
+    <row r="126" ht="13"/>
+    <row r="127" ht="13"/>
+    <row r="128" ht="13"/>
+    <row r="129" ht="13"/>
+    <row r="130" ht="13"/>
+    <row r="131" ht="13"/>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -14860,7 +13791,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
@@ -14874,7 +13805,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
@@ -14888,7 +13819,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -14902,7 +13833,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -14916,7 +13847,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -14930,7 +13861,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -14944,7 +13875,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -14958,7 +13889,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -14972,7 +13903,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -14986,7 +13917,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="12">
@@ -14994,13 +13925,13 @@
         <v>589</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>843</v>
+        <v>867</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="13">
@@ -15008,13 +13939,13 @@
         <v>589</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>844</v>
+        <v>868</v>
       </c>
       <c r="C13" s="4">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="14">
@@ -15022,13 +13953,13 @@
         <v>589</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>845</v>
+        <v>869</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="15">
@@ -15036,13 +13967,13 @@
         <v>589</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>846</v>
+        <v>870</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="16">
@@ -15056,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="17">
@@ -15070,7 +14001,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="18">
@@ -15078,13 +14009,13 @@
         <v>589</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>847</v>
+        <v>871</v>
       </c>
       <c r="C18" s="4">
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="19">
@@ -15092,13 +14023,13 @@
         <v>27</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="C19" s="4">
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="20">
@@ -15106,13 +14037,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="C20" s="4">
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="21">
@@ -15126,7 +14057,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="22">
@@ -15140,7 +14071,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="23">
@@ -15154,7 +14085,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="24">
@@ -15162,13 +14093,13 @@
         <v>529</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>850</v>
+        <v>874</v>
       </c>
       <c r="C24" s="4">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="25">
@@ -15176,13 +14107,13 @@
         <v>529</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>851</v>
+        <v>875</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="26">
@@ -15190,13 +14121,13 @@
         <v>529</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="27">
@@ -15204,13 +14135,13 @@
         <v>529</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="C27" s="4">
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="28">
@@ -15218,13 +14149,13 @@
         <v>529</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="C28" s="4">
         <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="29">
@@ -15232,13 +14163,13 @@
         <v>529</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>855</v>
+        <v>879</v>
       </c>
       <c r="C29" s="4">
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="30">
@@ -15246,13 +14177,13 @@
         <v>529</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>856</v>
+        <v>880</v>
       </c>
       <c r="C30" s="4">
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="31">
@@ -15260,13 +14191,13 @@
         <v>529</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>857</v>
+        <v>881</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="32">
@@ -15280,7 +14211,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="33">
@@ -15294,7 +14225,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="34">
@@ -15308,7 +14239,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="35">
@@ -15322,7 +14253,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="36">
@@ -15336,7 +14267,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="37">
@@ -15350,7 +14281,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="38">
@@ -15364,7 +14295,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="39">
@@ -15378,7 +14309,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="40">
@@ -15392,7 +14323,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="41">
@@ -15400,13 +14331,13 @@
         <v>438</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="C41" s="4">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="42">
@@ -15414,13 +14345,13 @@
         <v>438</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>859</v>
+        <v>883</v>
       </c>
       <c r="C42" s="4">
         <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="43">
@@ -15428,13 +14359,13 @@
         <v>438</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="C43" s="4">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="44">
@@ -15442,13 +14373,13 @@
         <v>438</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>861</v>
+        <v>885</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="45">
@@ -15456,13 +14387,13 @@
         <v>438</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>862</v>
+        <v>886</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="46">
@@ -15476,7 +14407,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="47">
@@ -15490,7 +14421,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="48">
@@ -15498,13 +14429,13 @@
         <v>126</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>863</v>
+        <v>887</v>
       </c>
       <c r="C48" s="4">
         <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="49">
@@ -15512,13 +14443,13 @@
         <v>126</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>857</v>
+        <v>881</v>
       </c>
       <c r="C49" s="4">
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="50">
@@ -15526,13 +14457,13 @@
         <v>126</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>864</v>
+        <v>888</v>
       </c>
       <c r="C50" s="4">
         <v>1</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="51">
@@ -15540,13 +14471,13 @@
         <v>126</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>851</v>
+        <v>875</v>
       </c>
       <c r="C51" s="4">
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="52">
@@ -15554,13 +14485,13 @@
         <v>126</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>865</v>
+        <v>889</v>
       </c>
       <c r="C52" s="4">
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="53">
@@ -15568,13 +14499,13 @@
         <v>126</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="C53" s="4">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>866</v>
-      </c>
-      <c r="C53" s="4">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="54">
@@ -15588,26 +14519,26 @@
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>845</v>
+        <v>869</v>
       </c>
       <c r="C55" s="4">
         <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>245</v>
@@ -15616,54 +14547,54 @@
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>868</v>
+        <v>892</v>
       </c>
       <c r="C57" s="4">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>869</v>
+        <v>893</v>
       </c>
       <c r="C58" s="4">
         <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>870</v>
+        <v>894</v>
       </c>
       <c r="C59" s="4">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>685</v>
@@ -15672,21 +14603,21 @@
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>871</v>
+        <v>895</v>
       </c>
       <c r="C61" s="4">
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="62" ht="13">
@@ -15700,7 +14631,7 @@
         <v>3</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="63" ht="13">
@@ -15708,13 +14639,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>872</v>
+        <v>896</v>
       </c>
       <c r="C63" s="2">
         <v>2</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="64" ht="13">
@@ -15722,13 +14653,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>873</v>
+        <v>897</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="65" ht="13">
@@ -15736,13 +14667,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>874</v>
+        <v>898</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="66" ht="13">
@@ -15756,7 +14687,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="67" ht="13">
@@ -15770,7 +14701,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="68" ht="13">
@@ -15784,7 +14715,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="69" ht="13">
@@ -15798,7 +14729,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="70" ht="13">
@@ -15812,7 +14743,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="71" ht="13">
@@ -15826,7 +14757,7 @@
         <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="72" ht="13">
@@ -15840,7 +14771,7 @@
         <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="73" ht="13">
@@ -15854,7 +14785,7 @@
         <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="74" ht="13">
@@ -15868,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="75" ht="13">
@@ -15882,7 +14813,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="76">
@@ -15890,13 +14821,13 @@
         <v>179</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>875</v>
+        <v>899</v>
       </c>
       <c r="C76" s="4">
         <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="77">
@@ -15904,13 +14835,13 @@
         <v>179</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>876</v>
+        <v>900</v>
       </c>
       <c r="C77" s="4">
         <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="78">
@@ -15918,13 +14849,13 @@
         <v>179</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>877</v>
+        <v>901</v>
       </c>
       <c r="C78" s="4">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="79">
@@ -15938,7 +14869,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="80">
@@ -15952,7 +14883,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="81">
@@ -15960,13 +14891,13 @@
         <v>179</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>878</v>
+        <v>902</v>
       </c>
       <c r="C81" s="4">
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="82">
@@ -15974,13 +14905,13 @@
         <v>179</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>879</v>
+        <v>903</v>
       </c>
       <c r="C82" s="4">
         <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="83">
@@ -15988,13 +14919,13 @@
         <v>179</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>880</v>
+        <v>904</v>
       </c>
       <c r="C83" s="4">
         <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="84">
@@ -16008,7 +14939,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="85">
@@ -16016,13 +14947,13 @@
         <v>179</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="C85" s="4">
         <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="86" ht="13">
@@ -16036,7 +14967,7 @@
         <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="87" ht="13">
@@ -16050,7 +14981,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="88" ht="13">
@@ -16064,7 +14995,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="89" ht="13">
@@ -16078,7 +15009,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="90" ht="13">
@@ -16092,110 +15023,110 @@
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>883</v>
+        <v>907</v>
       </c>
       <c r="C91" s="4">
         <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>884</v>
+        <v>908</v>
       </c>
       <c r="C92" s="4">
         <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>885</v>
+        <v>909</v>
       </c>
       <c r="C93" s="4">
         <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>886</v>
+        <v>910</v>
       </c>
       <c r="C94" s="4">
         <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>887</v>
+        <v>911</v>
       </c>
       <c r="C95" s="4">
         <v>1</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="C96" s="4">
         <v>1</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>889</v>
+        <v>913</v>
       </c>
       <c r="C97" s="4">
         <v>1</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>836</v>
@@ -16204,54 +15135,54 @@
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>890</v>
+        <v>914</v>
       </c>
       <c r="C99" s="4">
         <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>891</v>
+        <v>915</v>
       </c>
       <c r="C100" s="4">
         <v>2</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>893</v>
+        <v>917</v>
       </c>
       <c r="C101" s="4">
         <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>593</v>
@@ -16260,35 +15191,35 @@
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>892</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>894</v>
+        <v>916</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>918</v>
       </c>
       <c r="C103" s="4">
         <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>895</v>
+        <v>919</v>
       </c>
       <c r="C104" s="4">
         <v>3</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="105">
@@ -16302,7 +15233,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="106">
@@ -16316,7 +15247,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="107">
@@ -16330,7 +15261,7 @@
         <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="108">
@@ -16344,7 +15275,7 @@
         <v>1</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="109">
@@ -16358,7 +15289,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="110">
@@ -16372,7 +15303,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="111">
@@ -16386,7 +15317,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="112">
@@ -16400,7 +15331,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="113">
@@ -16414,7 +15345,7 @@
         <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="114">
@@ -16428,7 +15359,7 @@
         <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="115" ht="13">
@@ -16442,7 +15373,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="116" ht="13">
@@ -16456,7 +15387,7 @@
         <v>2</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="117" ht="13">
@@ -16470,7 +15401,7 @@
         <v>2</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="118" ht="13">
@@ -16484,7 +15415,7 @@
         <v>1</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="119" ht="13">
@@ -16498,7 +15429,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="120" ht="13">
@@ -16512,7 +15443,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="121" ht="13">
@@ -16526,7 +15457,7 @@
         <v>2</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="122" ht="13">
@@ -16540,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="123" ht="13">
@@ -16554,7 +15485,7 @@
         <v>2</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="124" ht="13">
@@ -16568,7 +15499,7 @@
         <v>2</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="125" ht="13">
@@ -16582,7 +15513,7 @@
         <v>2</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="126" ht="13">
@@ -16596,7 +15527,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
     <row r="127" ht="13">
@@ -16610,7 +15541,7 @@
         <v>3</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
     </row>
   </sheetData>
@@ -17362,13 +16293,13 @@
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="8" t="s">
-        <v>896</v>
-      </c>
-      <c r="B53" s="8" t="s">
+      <c r="A53" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="9">
         <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -17376,13 +16307,13 @@
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="8" t="s">
-        <v>896</v>
-      </c>
-      <c r="B54" s="8" t="s">
+      <c r="A54" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="9">
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -17390,13 +16321,13 @@
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="8" t="s">
-        <v>896</v>
-      </c>
-      <c r="B55" s="8" t="s">
+      <c r="A55" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="B55" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="9">
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -17404,13 +16335,13 @@
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="8" t="s">
-        <v>896</v>
-      </c>
-      <c r="B56" s="8" t="s">
+      <c r="A56" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="9">
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -17418,13 +16349,13 @@
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="8" t="s">
-        <v>897</v>
-      </c>
-      <c r="B57" s="8" t="s">
+      <c r="A57" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="B57" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="9">
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -17432,13 +16363,13 @@
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="8" t="s">
-        <v>897</v>
-      </c>
-      <c r="B58" s="8" t="s">
+      <c r="A58" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="9">
         <v>1</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -17446,13 +16377,13 @@
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="8" t="s">
-        <v>897</v>
-      </c>
-      <c r="B59" s="8" t="s">
+      <c r="A59" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="B59" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="9">
         <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -17460,13 +16391,13 @@
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="8" t="s">
-        <v>898</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>899</v>
-      </c>
-      <c r="C60" s="8">
+      <c r="A60" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="C60" s="9">
         <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -17474,13 +16405,13 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="8" t="s">
-        <v>898</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>849</v>
-      </c>
-      <c r="C61" s="8">
+      <c r="A61" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>873</v>
+      </c>
+      <c r="C61" s="9">
         <v>1</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -17488,13 +16419,13 @@
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="8" t="s">
-        <v>898</v>
-      </c>
-      <c r="B62" s="8" t="s">
+      <c r="A62" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B62" s="9" t="s">
         <v>827</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C62" s="9">
         <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -17502,13 +16433,13 @@
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>901</v>
-      </c>
-      <c r="C63" s="8">
+      <c r="A63" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="C63" s="9">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -17516,13 +16447,13 @@
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>902</v>
-      </c>
-      <c r="C64" s="8">
+      <c r="A64" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="C64" s="9">
         <v>1</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -17530,13 +16461,13 @@
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="B65" s="8" t="s">
+      <c r="A65" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="B65" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="9">
         <v>1</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -17544,13 +16475,13 @@
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="B66" s="8" t="s">
+      <c r="A66" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="B66" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="9">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -17558,13 +16489,13 @@
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="8" t="s">
-        <v>903</v>
-      </c>
-      <c r="B67" s="8" t="s">
+      <c r="A67" s="9" t="s">
+        <v>927</v>
+      </c>
+      <c r="B67" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="9">
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -17572,13 +16503,13 @@
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="8" t="s">
-        <v>903</v>
-      </c>
-      <c r="B68" s="8" t="s">
+      <c r="A68" s="9" t="s">
+        <v>927</v>
+      </c>
+      <c r="B68" s="9" t="s">
         <v>745</v>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="9">
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -17586,13 +16517,13 @@
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="8" t="s">
-        <v>903</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>904</v>
-      </c>
-      <c r="C69" s="8">
+      <c r="A69" s="9" t="s">
+        <v>927</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>928</v>
+      </c>
+      <c r="C69" s="9">
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">

--- a/ShinyApp/datasets/scinfer_combined_hs.xlsx
+++ b/ShinyApp/datasets/scinfer_combined_hs.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="928">
   <si>
     <t>celltype</t>
   </si>
@@ -2621,9 +2621,6 @@
   </si>
   <si>
     <t>CD1C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fibroblasts / Mesenchymal</t>
   </si>
   <si>
     <t>Heart</t>
@@ -2846,7 +2843,6 @@
     </font>
     <font>
       <sz val="7.500000"/>
-      <color indexed="64"/>
       <name val="Liberation Sans"/>
     </font>
   </fonts>
@@ -13617,48 +13613,9 @@
         <v>221</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="7" t="s">
-        <v>865</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="C41" s="1">
-        <v>1</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="7" t="s">
-        <v>865</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="C42" s="1">
-        <v>1</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="7" t="s">
-        <v>865</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="15" customHeight="1"/>
     <row r="44" ht="15" customHeight="1"/>
     <row r="45" ht="15" customHeight="1"/>
     <row r="46" ht="13"/>
@@ -13791,7 +13748,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
@@ -13805,7 +13762,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
@@ -13819,7 +13776,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -13833,7 +13790,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -13847,7 +13804,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -13861,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -13875,7 +13832,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -13889,7 +13846,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -13903,7 +13860,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -13917,7 +13874,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="12">
@@ -13925,13 +13882,13 @@
         <v>589</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="13">
@@ -13939,13 +13896,13 @@
         <v>589</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C13" s="4">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="14">
@@ -13953,13 +13910,13 @@
         <v>589</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="15">
@@ -13967,13 +13924,13 @@
         <v>589</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="16">
@@ -13987,7 +13944,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="17">
@@ -14001,7 +13958,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="18">
@@ -14009,13 +13966,13 @@
         <v>589</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C18" s="4">
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="19">
@@ -14023,13 +13980,13 @@
         <v>27</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C19" s="4">
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="20">
@@ -14037,13 +13994,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C20" s="4">
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="21">
@@ -14057,7 +14014,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="22">
@@ -14071,7 +14028,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="23">
@@ -14085,7 +14042,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="24">
@@ -14093,13 +14050,13 @@
         <v>529</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C24" s="4">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="25">
@@ -14107,13 +14064,13 @@
         <v>529</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26">
@@ -14121,13 +14078,13 @@
         <v>529</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="27">
@@ -14135,13 +14092,13 @@
         <v>529</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C27" s="4">
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="28">
@@ -14149,13 +14106,13 @@
         <v>529</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C28" s="4">
         <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="29">
@@ -14163,13 +14120,13 @@
         <v>529</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C29" s="4">
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="30">
@@ -14177,13 +14134,13 @@
         <v>529</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C30" s="4">
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="31">
@@ -14191,13 +14148,13 @@
         <v>529</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="32">
@@ -14211,7 +14168,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="33">
@@ -14225,7 +14182,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="34">
@@ -14239,7 +14196,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="35">
@@ -14253,7 +14210,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="36">
@@ -14267,7 +14224,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="37">
@@ -14281,7 +14238,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="38">
@@ -14295,7 +14252,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="39">
@@ -14309,7 +14266,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="40">
@@ -14323,7 +14280,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="41">
@@ -14331,13 +14288,13 @@
         <v>438</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C41" s="4">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="42">
@@ -14345,13 +14302,13 @@
         <v>438</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C42" s="4">
         <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="43">
@@ -14359,13 +14316,13 @@
         <v>438</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C43" s="4">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="44">
@@ -14373,13 +14330,13 @@
         <v>438</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="45">
@@ -14387,13 +14344,13 @@
         <v>438</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="46">
@@ -14407,7 +14364,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="47">
@@ -14421,7 +14378,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="48">
@@ -14429,13 +14386,13 @@
         <v>126</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C48" s="4">
         <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="49">
@@ -14443,13 +14400,13 @@
         <v>126</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C49" s="4">
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="50">
@@ -14457,13 +14414,13 @@
         <v>126</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C50" s="4">
         <v>1</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="51">
@@ -14471,13 +14428,13 @@
         <v>126</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C51" s="4">
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="52">
@@ -14485,13 +14442,13 @@
         <v>126</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C52" s="4">
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="53">
@@ -14499,13 +14456,13 @@
         <v>126</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C53" s="4">
         <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="54">
@@ -14519,26 +14476,26 @@
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C55" s="4">
         <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>245</v>
@@ -14547,54 +14504,54 @@
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>892</v>
-      </c>
       <c r="C57" s="4">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C58" s="4">
         <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C59" s="4">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>685</v>
@@ -14603,21 +14560,21 @@
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C61" s="4">
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="62" ht="13">
@@ -14631,7 +14588,7 @@
         <v>3</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="63" ht="13">
@@ -14639,13 +14596,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C63" s="2">
         <v>2</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="64" ht="13">
@@ -14653,13 +14610,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="65" ht="13">
@@ -14667,13 +14624,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="66" ht="13">
@@ -14687,7 +14644,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="67" ht="13">
@@ -14701,7 +14658,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="68" ht="13">
@@ -14715,7 +14672,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="69" ht="13">
@@ -14729,7 +14686,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="70" ht="13">
@@ -14743,7 +14700,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="71" ht="13">
@@ -14757,7 +14714,7 @@
         <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="72" ht="13">
@@ -14771,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="73" ht="13">
@@ -14785,7 +14742,7 @@
         <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="74" ht="13">
@@ -14799,7 +14756,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="75" ht="13">
@@ -14813,7 +14770,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="76">
@@ -14821,13 +14778,13 @@
         <v>179</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C76" s="4">
         <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="77">
@@ -14835,13 +14792,13 @@
         <v>179</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C77" s="4">
         <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="78">
@@ -14849,13 +14806,13 @@
         <v>179</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C78" s="4">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="79">
@@ -14869,7 +14826,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="80">
@@ -14883,7 +14840,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="81">
@@ -14891,13 +14848,13 @@
         <v>179</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C81" s="4">
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="82">
@@ -14905,13 +14862,13 @@
         <v>179</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C82" s="4">
         <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="83">
@@ -14919,13 +14876,13 @@
         <v>179</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C83" s="4">
         <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="84">
@@ -14939,7 +14896,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="85">
@@ -14947,13 +14904,13 @@
         <v>179</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C85" s="4">
         <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="86" ht="13">
@@ -14967,7 +14924,7 @@
         <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="87" ht="13">
@@ -14981,7 +14938,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="88" ht="13">
@@ -14995,7 +14952,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="89" ht="13">
@@ -15009,7 +14966,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="90" ht="13">
@@ -15023,110 +14980,110 @@
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>906</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>907</v>
-      </c>
       <c r="C91" s="4">
         <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C92" s="4">
         <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C93" s="4">
         <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C94" s="4">
         <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C95" s="4">
         <v>1</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C96" s="4">
         <v>1</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C97" s="4">
         <v>1</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>836</v>
@@ -15135,54 +15092,54 @@
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C99" s="4">
         <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C100" s="4">
         <v>2</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="B101" s="4" t="s">
-        <v>917</v>
-      </c>
       <c r="C101" s="4">
         <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>593</v>
@@ -15191,35 +15148,35 @@
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C103" s="4">
         <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C104" s="4">
         <v>3</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="105">
@@ -15233,7 +15190,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="106">
@@ -15247,7 +15204,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="107">
@@ -15261,7 +15218,7 @@
         <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="108">
@@ -15275,7 +15232,7 @@
         <v>1</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="109">
@@ -15289,7 +15246,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="110">
@@ -15303,7 +15260,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="111">
@@ -15317,7 +15274,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="112">
@@ -15331,7 +15288,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="113">
@@ -15345,7 +15302,7 @@
         <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="114">
@@ -15359,7 +15316,7 @@
         <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="115" ht="13">
@@ -15373,7 +15330,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="116" ht="13">
@@ -15387,7 +15344,7 @@
         <v>2</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="117" ht="13">
@@ -15401,7 +15358,7 @@
         <v>2</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="118" ht="13">
@@ -15415,7 +15372,7 @@
         <v>1</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="119" ht="13">
@@ -15429,7 +15386,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="120" ht="13">
@@ -15443,7 +15400,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="121" ht="13">
@@ -15457,7 +15414,7 @@
         <v>2</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="122" ht="13">
@@ -15471,7 +15428,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="123" ht="13">
@@ -15485,7 +15442,7 @@
         <v>2</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="124" ht="13">
@@ -15499,7 +15456,7 @@
         <v>2</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="125" ht="13">
@@ -15513,7 +15470,7 @@
         <v>2</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="126" ht="13">
@@ -15527,7 +15484,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="127" ht="13">
@@ -15541,7 +15498,7 @@
         <v>3</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -16294,7 +16251,7 @@
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>285</v>
@@ -16308,7 +16265,7 @@
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>83</v>
@@ -16322,7 +16279,7 @@
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>84</v>
@@ -16336,7 +16293,7 @@
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>325</v>
@@ -16350,7 +16307,7 @@
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="9" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>41</v>
@@ -16364,7 +16321,7 @@
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="9" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>323</v>
@@ -16378,7 +16335,7 @@
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="9" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>37</v>
@@ -16392,10 +16349,10 @@
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="B60" s="9" t="s">
         <v>922</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>923</v>
       </c>
       <c r="C60" s="9">
         <v>1</v>
@@ -16406,10 +16363,10 @@
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="9" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -16420,7 +16377,7 @@
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="9" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>827</v>
@@ -16434,10 +16391,10 @@
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="B63" s="9" t="s">
         <v>924</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>925</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -16448,10 +16405,10 @@
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="9" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C64" s="9">
         <v>1</v>
@@ -16462,7 +16419,7 @@
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="9" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>415</v>
@@ -16476,7 +16433,7 @@
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="9" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>131</v>
@@ -16490,7 +16447,7 @@
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="9" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>88</v>
@@ -16504,7 +16461,7 @@
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="9" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>745</v>
@@ -16518,10 +16475,10 @@
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="B69" s="9" t="s">
         <v>927</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>928</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
